--- a/main/ig/StructureDefinition-MESObservationPainSeverity.xlsx
+++ b/main/ig/StructureDefinition-MESObservationPainSeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T14:10:46+00:00</t>
+    <t>2026-03-12T14:12:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,7 +650,7 @@
     <t>MesReasonForMeasurement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.2.0}
 </t>
   </si>
   <si>
@@ -1655,7 +1655,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J159-MethodPainSeverity-ENS/FHIR/JDV-J159-MethodPainSeverity-ENS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J159-MethodPainSeverity-ENS/FHIR/JDV-J159-MethodPainSeverity-ENS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J159-MethodPainSeverity-ENS/FHIR/JDV-J159-MethodPainSeverity-ENS|20240927120000</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2414,7 +2414,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.76171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="89.29296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="99.29296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-MESObservationPainSeverity.xlsx
+++ b/main/ig/StructureDefinition-MESObservationPainSeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T14:12:24+00:00</t>
+    <t>2026-03-12T14:18:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
